--- a/data/rules/preNormalization.xlsx
+++ b/data/rules/preNormalization.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/VV_Python_Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/VV_Python_Project/data/rules/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41C697C-616E-0047-BF1B-5DB93EA2D230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03C5735-FC12-CF44-98FD-1143436BF6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="2220" windowWidth="27640" windowHeight="15920" xr2:uid="{664D7B0B-3A54-AB4A-9B2E-0F6BCF1A0441}"/>
+    <workbookView xWindow="1160" yWindow="1120" windowWidth="27640" windowHeight="15920" xr2:uid="{664D7B0B-3A54-AB4A-9B2E-0F6BCF1A0441}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,9 +52,6 @@
     <t>normalization_rule</t>
   </si>
   <si>
-    <t>DAFT</t>
-  </si>
-  <si>
     <t>Entity</t>
   </si>
   <si>
@@ -113,6 +110,9 @@
   </si>
   <si>
     <t>features.feature[].type.text</t>
+  </si>
+  <si>
+    <t>DFAT</t>
   </si>
 </sst>
 </file>
@@ -509,278 +509,278 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" s="2"/>
     </row>

--- a/data/rules/preNormalization.xlsx
+++ b/data/rules/preNormalization.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/VV_Python_Project/data/rules/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03C5735-FC12-CF44-98FD-1143436BF6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEDB887-9FE5-FC43-9C40-497FCEC6F759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="1120" windowWidth="27640" windowHeight="15920" xr2:uid="{664D7B0B-3A54-AB4A-9B2E-0F6BCF1A0441}"/>
+    <workbookView xWindow="10880" yWindow="1760" windowWidth="27640" windowHeight="15920" xr2:uid="{664D7B0B-3A54-AB4A-9B2E-0F6BCF1A0441}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="32">
   <si>
     <t>source</t>
   </si>
@@ -113,6 +113,24 @@
   </si>
   <si>
     <t>DFAT</t>
+  </si>
+  <si>
+    <t>EU-TRAVEL-BAN</t>
+  </si>
+  <si>
+    <t>nameAlias[].title</t>
+  </si>
+  <si>
+    <t>remove_list_markers</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>subjectType.code</t>
+  </si>
+  <si>
+    <t>person=Individual</t>
   </si>
 </sst>
 </file>
@@ -481,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD38AAAA-71AD-464E-BCF4-8B613DCBC998}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" customWidth="1"/>
@@ -784,6 +802,37 @@
       </c>
       <c r="E18" s="2"/>
     </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/data/rules/preNormalization.xlsx
+++ b/data/rules/preNormalization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/VV_Python_Project/data/rules/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEDB887-9FE5-FC43-9C40-497FCEC6F759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0EDADD-321D-BF4D-B660-A15A1FC34A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10880" yWindow="1760" windowWidth="27640" windowHeight="15920" xr2:uid="{664D7B0B-3A54-AB4A-9B2E-0F6BCF1A0441}"/>
+    <workbookView xWindow="8740" yWindow="500" windowWidth="27640" windowHeight="15920" xr2:uid="{664D7B0B-3A54-AB4A-9B2E-0F6BCF1A0441}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="36">
   <si>
     <t>source</t>
   </si>
@@ -131,6 +131,18 @@
   </si>
   <si>
     <t>person=Individual</t>
+  </si>
+  <si>
+    <t>UKSL</t>
+  </si>
+  <si>
+    <t>IndividualEntityShip</t>
+  </si>
+  <si>
+    <t>Ship</t>
+  </si>
+  <si>
+    <t>Ship=Vessel</t>
   </si>
 </sst>
 </file>
@@ -499,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD38AAAA-71AD-464E-BCF4-8B613DCBC998}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" customWidth="1"/>
@@ -772,7 +784,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -787,7 +799,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -802,7 +814,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -819,7 +831,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -832,6 +844,84 @@
       <c r="D20" t="s">
         <v>28</v>
       </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AA21" s="2"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
